--- a/FLORES DE ESTRADA/Diciembre/PRORRATEO Diciembre Estrada.xlsx
+++ b/FLORES DE ESTRADA/Diciembre/PRORRATEO Diciembre Estrada.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OneDrive\Desktop\RC CONSORCIO 2025\FLORES DE ESTRADA\Noviembre\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OneDrive\Desktop\RC CONSORCIO 2025\FLORES DE ESTRADA\Diciembre\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{27B3CB9A-F8B0-4676-92DE-B4411C79C2FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0ABF42E5-4B5C-466E-8632-A1CB2AED5D2B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="143" uniqueCount="83">
   <si>
     <t>Domicilio:</t>
   </si>
@@ -271,7 +271,10 @@
     <t>NN</t>
   </si>
   <si>
-    <t>EXPENSAS - VENCIMIENTO 14/12  LIQUIDACION : NOVIEMBRE</t>
+    <t>EXPENSAS - VENCIMIENTO 15/01  LIQUIDACION : DICIEMBRE</t>
+  </si>
+  <si>
+    <t>Romina</t>
   </si>
 </sst>
 </file>
@@ -609,7 +612,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="74">
+  <cellXfs count="73">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
@@ -744,8 +747,7 @@
     <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="1" fillId="3" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="9" fillId="3" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="5">
     <cellStyle name="Hipervínculo" xfId="3" builtinId="8"/>
@@ -1190,7 +1192,7 @@
         <v>56</v>
       </c>
       <c r="C7" s="50">
-        <v>1400000</v>
+        <v>1005203.7400000001</v>
       </c>
       <c r="D7" s="53"/>
       <c r="F7" s="7"/>
@@ -1306,7 +1308,7 @@
       </c>
       <c r="L11" s="5">
         <f>C7*E11/100</f>
-        <v>68600.000000000015</v>
+        <v>49254.983260000015</v>
       </c>
       <c r="M11" s="5">
         <f>C8*E11/100</f>
@@ -1314,7 +1316,7 @@
       </c>
       <c r="N11" s="44">
         <f>K11+L11+M11</f>
-        <v>68600.000000000015</v>
+        <v>49254.983260000015</v>
       </c>
     </row>
     <row r="12" spans="1:16" x14ac:dyDescent="0.25">
@@ -1334,27 +1336,27 @@
         <v>3.89</v>
       </c>
       <c r="F12" s="5">
-        <v>1236350.7065988535</v>
+        <v>1399609.5687795526</v>
       </c>
       <c r="G12" s="72"/>
       <c r="H12" s="8">
         <f t="shared" ref="H12:H34" si="0">F12-G12</f>
-        <v>1236350.7065988535</v>
+        <v>1399609.5687795526</v>
       </c>
       <c r="I12" s="5">
         <v>0</v>
       </c>
       <c r="J12" s="9">
         <f t="shared" ref="J12:J34" si="1">H12*8.8%</f>
-        <v>108798.86218069911</v>
+        <v>123165.64205260064</v>
       </c>
       <c r="K12" s="44">
         <f>H12+I12+J12</f>
-        <v>1345149.5687795526</v>
+        <v>1522775.2108321532</v>
       </c>
       <c r="L12" s="5">
         <f>C7*E12/100</f>
-        <v>54460</v>
+        <v>39102.425486</v>
       </c>
       <c r="M12" s="5">
         <f>C8*E12/100</f>
@@ -1362,7 +1364,7 @@
       </c>
       <c r="N12" s="44">
         <f>K12+L12+M12</f>
-        <v>1399609.5687795526</v>
+        <v>1561877.6363181532</v>
       </c>
     </row>
     <row r="13" spans="1:16" x14ac:dyDescent="0.25">
@@ -1405,7 +1407,7 @@
       </c>
       <c r="L13" s="5">
         <f>C7*E13/100</f>
-        <v>56000</v>
+        <v>40208.149600000004</v>
       </c>
       <c r="M13" s="5">
         <f>C8*E13/100</f>
@@ -1413,12 +1415,9 @@
       </c>
       <c r="N13" s="44">
         <f>K13+L13+M13</f>
-        <v>56000</v>
-      </c>
-      <c r="P13" s="64">
-        <f>G13+G30</f>
-        <v>72521</v>
-      </c>
+        <v>40208.149600000004</v>
+      </c>
+      <c r="P13" s="64"/>
     </row>
     <row r="14" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A14" s="11">
@@ -1440,7 +1439,7 @@
         <v>68600.000000000015</v>
       </c>
       <c r="G14" s="72">
-        <f t="shared" ref="G14" si="2">F14</f>
+        <f>F14</f>
         <v>68600.000000000015</v>
       </c>
       <c r="H14" s="8">
@@ -1460,15 +1459,15 @@
       </c>
       <c r="L14" s="5">
         <f>C7*E14/100</f>
-        <v>68600.000000000015</v>
+        <v>49254.983260000015</v>
       </c>
       <c r="M14" s="5">
         <f>C8*E14/100</f>
         <v>0</v>
       </c>
       <c r="N14" s="44">
-        <f t="shared" ref="N14:N24" si="3">K14+L14+M14</f>
-        <v>68600.000000000015</v>
+        <f t="shared" ref="N14:N24" si="2">K14+L14+M14</f>
+        <v>49254.983260000015</v>
       </c>
     </row>
     <row r="15" spans="1:16" x14ac:dyDescent="0.25">
@@ -1511,7 +1510,7 @@
       </c>
       <c r="L15" s="5">
         <f>C7*E15/100</f>
-        <v>54460</v>
+        <v>39102.425486</v>
       </c>
       <c r="M15" s="5">
         <f>C8*E15/100</f>
@@ -1519,7 +1518,7 @@
       </c>
       <c r="N15" s="44">
         <f>K15+L15+M15</f>
-        <v>54460</v>
+        <v>39102.425486</v>
       </c>
       <c r="P15" s="59"/>
     </row>
@@ -1533,40 +1532,44 @@
       <c r="C16" s="55" t="s">
         <v>9</v>
       </c>
-      <c r="D16" s="55"/>
+      <c r="D16" s="55" t="s">
+        <v>82</v>
+      </c>
       <c r="E16" s="3">
         <v>4</v>
       </c>
       <c r="F16" s="5">
-        <v>125206.60497127178</v>
-      </c>
-      <c r="G16" s="72"/>
+        <v>192224.7862087437</v>
+      </c>
+      <c r="G16" s="72">
+        <v>56000</v>
+      </c>
       <c r="H16" s="8">
         <f t="shared" si="0"/>
-        <v>125206.60497127178</v>
+        <v>136224.7862087437</v>
       </c>
       <c r="I16" s="5">
         <v>0</v>
       </c>
       <c r="J16" s="9">
         <f t="shared" si="1"/>
-        <v>11018.181237471917</v>
+        <v>11987.781186369446</v>
       </c>
       <c r="K16" s="44">
         <f>H16+J16+I16</f>
-        <v>136224.7862087437</v>
+        <v>148212.56739511315</v>
       </c>
       <c r="L16" s="5">
         <f>C7*E16/100</f>
-        <v>56000</v>
+        <v>40208.149600000004</v>
       </c>
       <c r="M16" s="5">
         <f>C8*E16/100</f>
         <v>0</v>
       </c>
       <c r="N16" s="44">
-        <f t="shared" si="3"/>
-        <v>192224.7862087437</v>
+        <f t="shared" si="2"/>
+        <v>188420.71699511315</v>
       </c>
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.25">
@@ -1589,7 +1592,7 @@
         <v>68600.000000000015</v>
       </c>
       <c r="G17" s="72">
-        <f t="shared" ref="G17:G21" si="4">F17</f>
+        <f>F17</f>
         <v>68600.000000000015</v>
       </c>
       <c r="H17" s="8">
@@ -1609,7 +1612,7 @@
       </c>
       <c r="L17" s="5">
         <f>C7*E17/100</f>
-        <v>68600.000000000015</v>
+        <v>49254.983260000015</v>
       </c>
       <c r="M17" s="5">
         <f>C8*E17/100</f>
@@ -1617,7 +1620,7 @@
       </c>
       <c r="N17" s="44">
         <f>K17+L17+M17</f>
-        <v>68600.000000000015</v>
+        <v>49254.983260000015</v>
       </c>
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.25">
@@ -1638,7 +1641,7 @@
         <v>54460</v>
       </c>
       <c r="G18" s="72">
-        <f t="shared" si="4"/>
+        <f t="shared" ref="G17:G21" si="3">F18</f>
         <v>54460</v>
       </c>
       <c r="H18" s="8">
@@ -1658,15 +1661,15 @@
       </c>
       <c r="L18" s="5">
         <f>C7*E18/100</f>
-        <v>54460</v>
+        <v>39102.425486</v>
       </c>
       <c r="M18" s="5">
         <f>C8*E18/100</f>
         <v>0</v>
       </c>
       <c r="N18" s="44">
-        <f t="shared" si="3"/>
-        <v>54460</v>
+        <f t="shared" si="2"/>
+        <v>39102.425486</v>
       </c>
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.25">
@@ -1689,7 +1692,7 @@
         <v>56000</v>
       </c>
       <c r="G19" s="72">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>56000</v>
       </c>
       <c r="H19" s="8">
@@ -1704,20 +1707,20 @@
         <v>0</v>
       </c>
       <c r="K19" s="44">
-        <f t="shared" ref="K19" si="5">H19+J19</f>
+        <f t="shared" ref="K19" si="4">H19+J19</f>
         <v>0</v>
       </c>
       <c r="L19" s="5">
         <f>C7*E19/100</f>
-        <v>56000</v>
+        <v>40208.149600000004</v>
       </c>
       <c r="M19" s="5">
         <f>C8*E19/100</f>
         <v>0</v>
       </c>
       <c r="N19" s="44">
-        <f t="shared" si="3"/>
-        <v>56000</v>
+        <f t="shared" si="2"/>
+        <v>40208.149600000004</v>
       </c>
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.25">
@@ -1758,7 +1761,7 @@
       </c>
       <c r="L20" s="5">
         <f>C7*E20/100</f>
-        <v>177240</v>
+        <v>127258.79348400002</v>
       </c>
       <c r="M20" s="5">
         <f>C8*E20/100</f>
@@ -1766,7 +1769,7 @@
       </c>
       <c r="N20" s="44">
         <f>K20+L20+M20</f>
-        <v>177240</v>
+        <v>127258.79348400002</v>
       </c>
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.25">
@@ -1788,8 +1791,8 @@
       <c r="F21" s="5">
         <v>108500</v>
       </c>
-      <c r="G21" s="73">
-        <f t="shared" si="4"/>
+      <c r="G21" s="72">
+        <f>F21</f>
         <v>108500</v>
       </c>
       <c r="H21" s="8">
@@ -1809,15 +1812,15 @@
       </c>
       <c r="L21" s="5">
         <f>C7*E21/100</f>
-        <v>108500</v>
+        <v>77903.289850000016</v>
       </c>
       <c r="M21" s="5">
         <f>C8*E21/100</f>
         <v>0</v>
       </c>
       <c r="N21" s="44">
-        <f t="shared" si="3"/>
-        <v>108500</v>
+        <f t="shared" si="2"/>
+        <v>77903.289850000016</v>
       </c>
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.25">
@@ -1835,35 +1838,38 @@
         <v>7.51</v>
       </c>
       <c r="F22" s="5">
-        <v>219532.32</v>
-      </c>
-      <c r="G22" s="72"/>
+        <v>343991.16416000004</v>
+      </c>
+      <c r="G22" s="72">
+        <f>F22</f>
+        <v>343991.16416000004</v>
+      </c>
       <c r="H22" s="8">
         <f t="shared" si="0"/>
-        <v>219532.32</v>
+        <v>0</v>
       </c>
       <c r="I22" s="5">
         <v>0</v>
       </c>
       <c r="J22" s="9">
         <f t="shared" si="1"/>
-        <v>19318.844160000004</v>
+        <v>0</v>
       </c>
       <c r="K22" s="44">
-        <f t="shared" ref="K22:K24" si="6">H22+J22+I22</f>
-        <v>238851.16416000001</v>
+        <f t="shared" ref="K22:K24" si="5">H22+J22+I22</f>
+        <v>0</v>
       </c>
       <c r="L22" s="5">
         <f>C7*E22/100</f>
-        <v>105140</v>
+        <v>75490.800874000008</v>
       </c>
       <c r="M22" s="5">
         <f>C8*E22/100</f>
         <v>0</v>
       </c>
       <c r="N22" s="44">
-        <f t="shared" si="3"/>
-        <v>343991.16416000004</v>
+        <f t="shared" si="2"/>
+        <v>75490.800874000008</v>
       </c>
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.25">
@@ -1881,30 +1887,27 @@
         <v>4.45</v>
       </c>
       <c r="F23" s="5">
-        <v>396935.46834557253</v>
-      </c>
-      <c r="G23" s="72">
-        <f>200000-63932</f>
-        <v>136068</v>
-      </c>
+        <v>346123.80555998289</v>
+      </c>
+      <c r="G23" s="72"/>
       <c r="H23" s="8">
         <f t="shared" si="0"/>
-        <v>260867.46834557253</v>
+        <v>346123.80555998289</v>
       </c>
       <c r="I23" s="5">
         <v>0</v>
       </c>
       <c r="J23" s="9">
         <f t="shared" si="1"/>
-        <v>22956.337214410385</v>
+        <v>30458.894889278497</v>
       </c>
       <c r="K23" s="44">
         <f>H23+J23+I23</f>
-        <v>283823.80555998289</v>
+        <v>376582.70044926141</v>
       </c>
       <c r="L23" s="5">
         <f>C7*E23/100</f>
-        <v>62300</v>
+        <v>44731.566430000013</v>
       </c>
       <c r="M23" s="5">
         <f>C8*E23/100</f>
@@ -1912,7 +1915,7 @@
       </c>
       <c r="N23" s="44">
         <f>K23+L23+M23</f>
-        <v>346123.80555998289</v>
+        <v>421314.26687926141</v>
       </c>
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.25">
@@ -1948,20 +1951,20 @@
         <v>0</v>
       </c>
       <c r="K24" s="44">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="L24" s="5">
         <f>C7*E24/100</f>
-        <v>86380</v>
+        <v>62021.070758000009</v>
       </c>
       <c r="M24" s="5">
         <f>C8*E24/100</f>
         <v>0</v>
       </c>
       <c r="N24" s="44">
-        <f t="shared" si="3"/>
-        <v>86380</v>
+        <f t="shared" si="2"/>
+        <v>62021.070758000009</v>
       </c>
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.25">
@@ -1981,29 +1984,29 @@
         <v>4.45</v>
       </c>
       <c r="F25" s="5">
-        <v>576539.46321001393</v>
+        <v>621792.44797249511</v>
       </c>
       <c r="G25" s="72">
         <v>62301</v>
       </c>
       <c r="H25" s="8">
         <f t="shared" si="0"/>
-        <v>514238.46321001393</v>
+        <v>559491.44797249511</v>
       </c>
       <c r="I25" s="5">
         <v>0</v>
       </c>
       <c r="J25" s="9">
         <f t="shared" si="1"/>
-        <v>45252.984762481232</v>
+        <v>49235.247421579574</v>
       </c>
       <c r="K25" s="44">
         <f>H25+J25+I25</f>
-        <v>559491.44797249511</v>
+        <v>608726.69539407466</v>
       </c>
       <c r="L25" s="5">
         <f>C7*E25/100+1</f>
-        <v>62301</v>
+        <v>44732.566430000013</v>
       </c>
       <c r="M25" s="5">
         <f>C8*E25/100</f>
@@ -2011,7 +2014,7 @@
       </c>
       <c r="N25" s="44">
         <f>K25+L25+M25</f>
-        <v>621792.44797249511</v>
+        <v>653459.26182407467</v>
       </c>
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.25">
@@ -2031,30 +2034,29 @@
         <v>9.19</v>
       </c>
       <c r="F26" s="5">
-        <v>1581331.9782616417</v>
+        <v>1763640.4643486661</v>
       </c>
       <c r="G26" s="72">
-        <f>189300.5-110707</f>
-        <v>78593.5</v>
+        <v>128661</v>
       </c>
       <c r="H26" s="8">
         <f t="shared" si="0"/>
-        <v>1502738.4782616417</v>
+        <v>1634979.4643486661</v>
       </c>
       <c r="I26" s="5">
         <v>0</v>
       </c>
       <c r="J26" s="9">
         <f t="shared" si="1"/>
-        <v>132240.98608702447</v>
+        <v>143878.19286268263</v>
       </c>
       <c r="K26" s="44">
         <f>H26+J26+I26</f>
-        <v>1634979.4643486661</v>
+        <v>1778857.6572113489</v>
       </c>
       <c r="L26" s="5">
         <f>C7*E26/100+1</f>
-        <v>128661</v>
+        <v>92379.223706000004</v>
       </c>
       <c r="M26" s="5">
         <f>C8*E26/100</f>
@@ -2062,7 +2064,7 @@
       </c>
       <c r="N26" s="44">
         <f>K26+L26+M26</f>
-        <v>1763640.4643486661</v>
+        <v>1871236.8809173489</v>
       </c>
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.25">
@@ -2100,12 +2102,12 @@
         <v>0</v>
       </c>
       <c r="K27" s="44">
-        <f t="shared" ref="K27:K34" si="7">H27+J27+I27</f>
+        <f t="shared" ref="K27:K34" si="6">H27+J27+I27</f>
         <v>0</v>
       </c>
       <c r="L27" s="5">
         <f>C7*E27/100+1</f>
-        <v>16521</v>
+        <v>11862.404132000001</v>
       </c>
       <c r="M27" s="5">
         <f>C8*E27/100</f>
@@ -2113,7 +2115,7 @@
       </c>
       <c r="N27" s="44">
         <f>K27+L27+M27</f>
-        <v>16521</v>
+        <v>11862.404132000001</v>
       </c>
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.25">
@@ -2131,35 +2133,35 @@
         <v>1.18</v>
       </c>
       <c r="F28" s="5">
-        <v>187626.0879476468</v>
+        <v>220658.18368703971</v>
       </c>
       <c r="G28" s="72"/>
       <c r="H28" s="8">
         <f t="shared" si="0"/>
-        <v>187626.0879476468</v>
+        <v>220658.18368703971</v>
       </c>
       <c r="I28" s="5">
         <v>0</v>
       </c>
       <c r="J28" s="9">
         <f t="shared" si="1"/>
-        <v>16511.09573939292</v>
+        <v>19417.920164459498</v>
       </c>
       <c r="K28" s="44">
-        <f t="shared" si="7"/>
-        <v>204137.18368703971</v>
+        <f t="shared" si="6"/>
+        <v>240076.10385149921</v>
       </c>
       <c r="L28" s="5">
         <f>C7*E28/100+1</f>
-        <v>16521</v>
+        <v>11862.404132000001</v>
       </c>
       <c r="M28" s="5">
         <f>C8*E28/100</f>
         <v>0</v>
       </c>
       <c r="N28" s="44">
-        <f t="shared" ref="N28:N34" si="8">K28+L28+M28</f>
-        <v>220658.18368703971</v>
+        <f t="shared" ref="N28:N34" si="7">K28+L28+M28</f>
+        <v>251938.50798349921</v>
       </c>
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.25">
@@ -2177,35 +2179,35 @@
         <v>1.18</v>
       </c>
       <c r="F29" s="5">
-        <v>187626.0879476468</v>
+        <v>220658.18368703971</v>
       </c>
       <c r="G29" s="72"/>
       <c r="H29" s="8">
         <f t="shared" si="0"/>
-        <v>187626.0879476468</v>
+        <v>220658.18368703971</v>
       </c>
       <c r="I29" s="5">
         <v>0</v>
       </c>
       <c r="J29" s="9">
         <f t="shared" si="1"/>
-        <v>16511.09573939292</v>
+        <v>19417.920164459498</v>
       </c>
       <c r="K29" s="44">
-        <f t="shared" si="7"/>
-        <v>204137.18368703971</v>
+        <f t="shared" si="6"/>
+        <v>240076.10385149921</v>
       </c>
       <c r="L29" s="5">
         <f>C7*E29/100+1</f>
-        <v>16521</v>
+        <v>11862.404132000001</v>
       </c>
       <c r="M29" s="5">
         <f>C8*E29/100</f>
         <v>0</v>
       </c>
       <c r="N29" s="44">
-        <f t="shared" si="8"/>
-        <v>220658.18368703971</v>
+        <f t="shared" si="7"/>
+        <v>251938.50798349921</v>
       </c>
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.25">
@@ -2241,12 +2243,12 @@
         <v>0</v>
       </c>
       <c r="K30" s="44">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="L30" s="5">
         <f>C7*E30/100+1</f>
-        <v>16521</v>
+        <v>11862.404132000001</v>
       </c>
       <c r="M30" s="5">
         <f>C8*E30/100</f>
@@ -2254,7 +2256,7 @@
       </c>
       <c r="N30" s="44">
         <f>K30+L30+M30</f>
-        <v>16521</v>
+        <v>11862.404132000001</v>
       </c>
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.25">
@@ -2275,7 +2277,7 @@
         <v>16521</v>
       </c>
       <c r="G31" s="72">
-        <f t="shared" ref="G31:G33" si="9">F31</f>
+        <f>F31</f>
         <v>16521</v>
       </c>
       <c r="H31" s="8">
@@ -2290,12 +2292,12 @@
         <v>0</v>
       </c>
       <c r="K31" s="44">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="L31" s="5">
         <f>C7*E31/100+1</f>
-        <v>16521</v>
+        <v>11862.404132000001</v>
       </c>
       <c r="M31" s="5">
         <f>C8*E31/100</f>
@@ -2303,7 +2305,7 @@
       </c>
       <c r="N31" s="44">
         <f>K31+L31+M31</f>
-        <v>16521</v>
+        <v>11862.404132000001</v>
       </c>
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.25">
@@ -2339,20 +2341,20 @@
         <v>0</v>
       </c>
       <c r="K32" s="44">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="L32" s="5">
         <f>C7*E32/100+1</f>
-        <v>16521</v>
+        <v>11862.404132000001</v>
       </c>
       <c r="M32" s="5">
         <f>C8*E32/100</f>
         <v>0</v>
       </c>
       <c r="N32" s="44">
-        <f t="shared" si="8"/>
-        <v>16521</v>
+        <f t="shared" si="7"/>
+        <v>11862.404132000001</v>
       </c>
     </row>
     <row r="33" spans="1:15" x14ac:dyDescent="0.25">
@@ -2370,27 +2372,27 @@
         <v>1.18</v>
       </c>
       <c r="F33" s="5">
-        <v>16521</v>
+        <v>34495.847999999998</v>
       </c>
       <c r="G33" s="72"/>
       <c r="H33" s="8">
         <f t="shared" si="0"/>
-        <v>16521</v>
+        <v>34495.847999999998</v>
       </c>
       <c r="I33" s="5">
         <v>0</v>
       </c>
       <c r="J33" s="9">
         <f t="shared" si="1"/>
-        <v>1453.8480000000002</v>
+        <v>3035.6346240000003</v>
       </c>
       <c r="K33" s="44">
-        <f t="shared" si="7"/>
-        <v>17974.848000000002</v>
+        <f t="shared" si="6"/>
+        <v>37531.482623999997</v>
       </c>
       <c r="L33" s="5">
         <f>C7*E33/100+1</f>
-        <v>16521</v>
+        <v>11862.404132000001</v>
       </c>
       <c r="M33" s="5">
         <f>C8*E33/100</f>
@@ -2398,7 +2400,7 @@
       </c>
       <c r="N33" s="44">
         <f>K33+L33+M33</f>
-        <v>34495.847999999998</v>
+        <v>49393.886756</v>
       </c>
       <c r="O33" s="59"/>
     </row>
@@ -2417,35 +2419,38 @@
         <v>1.18</v>
       </c>
       <c r="F34" s="5">
-        <v>34495.847999999998</v>
-      </c>
-      <c r="G34" s="72"/>
+        <v>54052.482623999997</v>
+      </c>
+      <c r="G34" s="72">
+        <f>F34</f>
+        <v>54052.482623999997</v>
+      </c>
       <c r="H34" s="8">
         <f t="shared" si="0"/>
-        <v>34495.847999999998</v>
+        <v>0</v>
       </c>
       <c r="I34" s="5">
         <v>0</v>
       </c>
       <c r="J34" s="9">
         <f t="shared" si="1"/>
-        <v>3035.6346240000003</v>
+        <v>0</v>
       </c>
       <c r="K34" s="44">
-        <f t="shared" si="7"/>
-        <v>37531.482623999997</v>
+        <f t="shared" si="6"/>
+        <v>0</v>
       </c>
       <c r="L34" s="5">
         <f>C7*E34/100+1</f>
-        <v>16521</v>
+        <v>11862.404132000001</v>
       </c>
       <c r="M34" s="5">
         <f>C8*E34/100</f>
         <v>0</v>
       </c>
       <c r="N34" s="44">
-        <f t="shared" si="8"/>
-        <v>54052.482623999997</v>
+        <f t="shared" si="7"/>
+        <v>11862.404132000001</v>
       </c>
     </row>
     <row r="35" spans="1:15" s="4" customFormat="1" ht="21" x14ac:dyDescent="0.35">
@@ -2461,15 +2466,15 @@
       </c>
       <c r="F35" s="46">
         <f>SUM(F11:F34)</f>
-        <v>5427089.5652826475</v>
+        <v>6062170.9350275202</v>
       </c>
       <c r="G35" s="61">
         <f>SUM(G11:G34)</f>
-        <v>1141886.5</v>
+        <v>1509929.6467840001</v>
       </c>
       <c r="H35" s="47">
         <f>SUM(H11:H34)</f>
-        <v>4285203.0652826475</v>
+        <v>4552241.2882435201</v>
       </c>
       <c r="I35" s="47">
         <f>SUM(I12:I34)</f>
@@ -2477,12 +2482,12 @@
       </c>
       <c r="J35" s="48">
         <f>SUM(J11:J34)</f>
-        <v>377097.86974487297</v>
+        <v>400597.23336542974</v>
       </c>
       <c r="K35" s="48"/>
       <c r="L35" s="47">
         <f>SUM(L11:L34)</f>
-        <v>1399870</v>
+        <v>1005113.2196260006</v>
       </c>
       <c r="M35" s="51">
         <f>SUM(M11:M34)</f>
@@ -2490,7 +2495,7 @@
       </c>
       <c r="N35" s="56">
         <f>SUM(N11:N34)</f>
-        <v>6062170.9350275202</v>
+        <v>5957951.7412349507</v>
       </c>
     </row>
     <row r="36" spans="1:15" x14ac:dyDescent="0.25">
